--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.93491683640989</v>
+        <v>6.814423985916608</v>
       </c>
       <c r="D2" t="n">
-        <v>41.90682090352053</v>
+        <v>6.809858396822086</v>
       </c>
       <c r="E2" t="n">
-        <v>7.169365345615586</v>
+        <v>1.165021868662533</v>
       </c>
       <c r="F2" t="n">
-        <v>7.442557528744454</v>
+        <v>1.209415598420974</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.35828198348832</v>
+        <v>8.020720822316852</v>
       </c>
       <c r="D3" t="n">
-        <v>48.94909327410008</v>
+        <v>7.954227657041264</v>
       </c>
       <c r="E3" t="n">
-        <v>7.169365345615586</v>
+        <v>1.165021868662533</v>
       </c>
       <c r="F3" t="n">
-        <v>7.442557528744454</v>
+        <v>1.209415598420974</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.44596407521779</v>
+        <v>7.059969162222891</v>
       </c>
       <c r="D4" t="n">
-        <v>42.89094920869922</v>
+        <v>6.969779246413624</v>
       </c>
       <c r="E4" t="n">
-        <v>7.169365345615586</v>
+        <v>1.165021868662533</v>
       </c>
       <c r="F4" t="n">
-        <v>7.442557528744454</v>
+        <v>1.209415598420974</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.86207003389158</v>
+        <v>5.502586380507381</v>
       </c>
       <c r="D5" t="n">
-        <v>32.98797203425499</v>
+        <v>5.360545455566435</v>
       </c>
       <c r="E5" t="n">
-        <v>7.169365345615586</v>
+        <v>1.165021868662533</v>
       </c>
       <c r="F5" t="n">
-        <v>7.442557528744454</v>
+        <v>1.209415598420974</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.0660777736301</v>
+        <v>5.860737638214891</v>
       </c>
       <c r="D6" t="n">
-        <v>25.89140587065877</v>
+        <v>4.207353453982051</v>
       </c>
       <c r="E6" t="n">
-        <v>7.169365345615586</v>
+        <v>1.165021868662533</v>
       </c>
       <c r="F6" t="n">
-        <v>7.442557528744454</v>
+        <v>1.209415598420974</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.63351818361721</v>
+        <v>8.877946704837797</v>
       </c>
       <c r="D7" t="n">
-        <v>40.39831548552384</v>
+        <v>6.564726266397624</v>
       </c>
       <c r="E7" t="n">
-        <v>7.169365345615586</v>
+        <v>1.165021868662533</v>
       </c>
       <c r="F7" t="n">
-        <v>7.442557528744454</v>
+        <v>1.209415598420974</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
